--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112181718</v>
+        <v>135431666</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489869</v>
+        <v>490127</v>
       </c>
       <c r="R2" t="n">
-        <v>6847851</v>
+        <v>6848356</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,15 +760,2743 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135430496</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>490087</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6848091</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112181718</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489869</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6847851</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135428817</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489686</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6848174</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135429631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489885</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6848133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135430122</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490038</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6848065</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135431705</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490106</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6848374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135429557</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489799</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6848087</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135429817</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489942</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6848149</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135430711</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6848129</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135430823</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490043</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6848215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135431271</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6848240</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135431283</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490151</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6848231</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135429232</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489785</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6848000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135430208</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6848121</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135430251</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490055</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6848127</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135430270</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490037</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6848115</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135430474</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490087</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6848100</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135430855</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6848206</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135431313</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490147</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6848240</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135431477</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6848351</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135431652</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6848345</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135431942</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6848436</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135432247</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490053</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6848327</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135432573</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>489761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6848218</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135430638</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6848138</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135430729</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6848135</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135430884</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6848204</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429631</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429817</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430823</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431283</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429232</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430208</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430251</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2412,6 +2497,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430270</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2509,6 +2599,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430474</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430855</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2703,6 +2803,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431313</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431477</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431652</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3003,6 +3118,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431942</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432247</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432573</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3303,6 +3433,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430638</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3400,6 +3535,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430729</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3497,8 +3637,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135431666</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135430496</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135428817</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>135429631</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135430122</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135431705</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135429557</v>
       </c>
       <c r="B9" t="n">
-        <v>58410</v>
+        <v>58415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>135429817</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>135430711</v>
       </c>
       <c r="B11" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>135430823</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>135431271</v>
       </c>
       <c r="B13" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>135431283</v>
       </c>
       <c r="B14" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>135429232</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135430208</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>135430251</v>
       </c>
       <c r="B17" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135430270</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>135430474</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135430855</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135431313</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135431477</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135431652</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>135431942</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135432247</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135432573</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>135430638</v>
       </c>
       <c r="B27" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135430729</v>
       </c>
       <c r="B28" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135430884</v>
       </c>
       <c r="B29" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135431666</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135430496</v>
       </c>
       <c r="B3" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>135429817</v>
       </c>
       <c r="B10" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>135430711</v>
       </c>
       <c r="B11" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>135430823</v>
       </c>
       <c r="B12" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>135431271</v>
       </c>
       <c r="B13" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>135431283</v>
       </c>
       <c r="B14" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>135429232</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135430208</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>135430251</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135430270</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>135430474</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135430855</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135431313</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135431477</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135431652</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>135431942</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135432247</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135432573</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>135430638</v>
       </c>
       <c r="B27" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135430729</v>
       </c>
       <c r="B28" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135430884</v>
       </c>
       <c r="B29" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112181718</v>
+        <v>135431666</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489869</v>
+        <v>490127</v>
       </c>
       <c r="R2" t="n">
-        <v>6847851</v>
+        <v>6848356</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,24 +765,2914 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135431666</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135430496</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>490087</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6848091</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430496</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112181718</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489869</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6847851</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/112181718</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135428817</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489686</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6848174</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428817</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135429631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489885</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6848133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429631</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135430122</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490038</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6848065</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430122</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135431705</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490106</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6848374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431705</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135429557</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58415</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489799</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6848087</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429557</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135429817</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489942</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6848149</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429817</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135430711</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6848129</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430711</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135430823</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490043</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6848215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430823</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135431271</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99309</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6848240</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431271</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135431283</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99309</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490151</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6848231</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431283</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135429232</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489785</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6848000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429232</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135430208</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6848121</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430208</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135430251</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490055</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6848127</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430251</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135430270</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490037</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6848115</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430270</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135430474</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490087</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6848100</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430474</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135430855</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6848206</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430855</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135431313</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490147</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6848240</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431313</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135431477</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6848351</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431477</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135431652</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6848345</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431652</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135431942</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6848436</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431942</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135432247</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490053</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6848327</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432247</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135432573</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>489761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6848218</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432573</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135430638</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99192</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6848138</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430638</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135430729</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99192</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6848135</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430729</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135430884</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99192</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6848204</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430884</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>135429817</v>
       </c>
       <c r="B10" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>135430711</v>
       </c>
       <c r="B11" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>135430823</v>
       </c>
       <c r="B12" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>135431271</v>
       </c>
       <c r="B13" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>135431283</v>
       </c>
       <c r="B14" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>135429232</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135430208</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>135430251</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135430270</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>135430474</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135430855</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135431313</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135431477</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135431652</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>135431942</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135432247</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135432573</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>135430638</v>
       </c>
       <c r="B27" t="n">
-        <v>99192</v>
+        <v>99194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135430729</v>
       </c>
       <c r="B28" t="n">
-        <v>99192</v>
+        <v>99194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135430884</v>
       </c>
       <c r="B29" t="n">
-        <v>99192</v>
+        <v>99194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112181718</v>
+        <v>136042902</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489869</v>
+        <v>489554</v>
       </c>
       <c r="R4" t="n">
-        <v>6847851</v>
+        <v>6848182</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -989,63 +989,58 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112181718</t>
+          <t>https://artportalen.se/Sighting/136042902</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135428817</v>
+        <v>136042905</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>79200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489686</v>
+        <v>489724</v>
       </c>
       <c r="R5" t="n">
-        <v>6848174</v>
+        <v>6848320</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1064,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,80 +1089,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135428817</t>
+          <t>https://artportalen.se/Sighting/136042905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135429631</v>
+        <v>112181718</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489885</v>
+        <v>489869</v>
       </c>
       <c r="R6" t="n">
-        <v>6848133</v>
+        <v>6847851</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,12 +1175,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,80 +1200,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429631</t>
+          <t>https://artportalen.se/Sighting/112181718</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135430122</v>
+        <v>136042901</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490038</v>
+        <v>489542</v>
       </c>
       <c r="R7" t="n">
-        <v>6848065</v>
+        <v>6848201</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1286,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,24 +1311,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430122</t>
+          <t>https://artportalen.se/Sighting/136042901</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135431705</v>
+        <v>135428817</v>
       </c>
       <c r="B8" t="n">
         <v>57167</v>
@@ -1368,35 +1356,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490106</v>
+        <v>489686</v>
       </c>
       <c r="R8" t="n">
-        <v>6848374</v>
+        <v>6848174</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,53 +1433,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431705</t>
+          <t>https://artportalen.se/Sighting/135428817</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135429557</v>
+        <v>135429631</v>
       </c>
       <c r="B9" t="n">
-        <v>58415</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1506,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489799</v>
+        <v>489885</v>
       </c>
       <c r="R9" t="n">
-        <v>6848087</v>
+        <v>6848133</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1553,11 +1536,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1572,16 +1550,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429557</t>
+          <t>https://artportalen.se/Sighting/135429631</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135429817</v>
+        <v>135430122</v>
       </c>
       <c r="B10" t="n">
-        <v>99193</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,37 +1567,52 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489942</v>
+        <v>490038</v>
       </c>
       <c r="R10" t="n">
-        <v>6848149</v>
+        <v>6848065</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,16 +1667,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429817</t>
+          <t>https://artportalen.se/Sighting/135430122</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135430711</v>
+        <v>135431705</v>
       </c>
       <c r="B11" t="n">
-        <v>99193</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,37 +1684,52 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489990</v>
+        <v>490106</v>
       </c>
       <c r="R11" t="n">
-        <v>6848129</v>
+        <v>6848374</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,54 +1784,68 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430711</t>
+          <t>https://artportalen.se/Sighting/135431705</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135430823</v>
+        <v>135429557</v>
       </c>
       <c r="B12" t="n">
-        <v>99193</v>
+        <v>58415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490043</v>
+        <v>489799</v>
       </c>
       <c r="R12" t="n">
-        <v>6848215</v>
+        <v>6848087</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,6 +1885,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1878,16 +1905,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430823</t>
+          <t>https://artportalen.se/Sighting/135429557</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135431271</v>
+        <v>135429817</v>
       </c>
       <c r="B13" t="n">
-        <v>99311</v>
+        <v>99193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1919,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490154</v>
+        <v>489942</v>
       </c>
       <c r="R13" t="n">
-        <v>6848240</v>
+        <v>6848149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,16 +2007,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431271</t>
+          <t>https://artportalen.se/Sighting/135429817</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135431283</v>
+        <v>135430711</v>
       </c>
       <c r="B14" t="n">
-        <v>99311</v>
+        <v>99193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490151</v>
+        <v>489990</v>
       </c>
       <c r="R14" t="n">
-        <v>6848231</v>
+        <v>6848129</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,60 +2109,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431283</t>
+          <t>https://artportalen.se/Sighting/135430711</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135429232</v>
+        <v>135430823</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489785</v>
+        <v>490043</v>
       </c>
       <c r="R15" t="n">
-        <v>6848000</v>
+        <v>6848215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,38 +2211,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429232</t>
+          <t>https://artportalen.se/Sighting/135430823</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135430208</v>
+        <v>135431271</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490064</v>
+        <v>490154</v>
       </c>
       <c r="R16" t="n">
-        <v>6848121</v>
+        <v>6848240</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,38 +2313,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430208</t>
+          <t>https://artportalen.se/Sighting/135431271</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135430251</v>
+        <v>135431283</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490055</v>
+        <v>490151</v>
       </c>
       <c r="R17" t="n">
-        <v>6848127</v>
+        <v>6848231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,13 +2415,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430251</t>
+          <t>https://artportalen.se/Sighting/135431283</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135430270</v>
+        <v>135429232</v>
       </c>
       <c r="B18" t="n">
         <v>99276</v>
@@ -2431,17 +2449,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490037</v>
+        <v>489785</v>
       </c>
       <c r="R18" t="n">
-        <v>6848115</v>
+        <v>6848000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,13 +2526,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430270</t>
+          <t>https://artportalen.se/Sighting/135429232</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135430474</v>
+        <v>135430208</v>
       </c>
       <c r="B19" t="n">
         <v>99276</v>
@@ -2540,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490087</v>
+        <v>490064</v>
       </c>
       <c r="R19" t="n">
-        <v>6848100</v>
+        <v>6848121</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,13 +2628,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430474</t>
+          <t>https://artportalen.se/Sighting/135430208</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135430855</v>
+        <v>135430251</v>
       </c>
       <c r="B20" t="n">
         <v>99276</v>
@@ -2642,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490054</v>
+        <v>490055</v>
       </c>
       <c r="R20" t="n">
-        <v>6848206</v>
+        <v>6848127</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,13 +2730,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430855</t>
+          <t>https://artportalen.se/Sighting/135430251</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135431313</v>
+        <v>135430270</v>
       </c>
       <c r="B21" t="n">
         <v>99276</v>
@@ -2744,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490147</v>
+        <v>490037</v>
       </c>
       <c r="R21" t="n">
-        <v>6848240</v>
+        <v>6848115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,13 +2832,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431313</t>
+          <t>https://artportalen.se/Sighting/135430270</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135431477</v>
+        <v>135430474</v>
       </c>
       <c r="B22" t="n">
         <v>99276</v>
@@ -2839,26 +2866,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490169</v>
+        <v>490087</v>
       </c>
       <c r="R22" t="n">
-        <v>6848351</v>
+        <v>6848100</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,13 +2934,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431477</t>
+          <t>https://artportalen.se/Sighting/135430474</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135431652</v>
+        <v>135430855</v>
       </c>
       <c r="B23" t="n">
         <v>99276</v>
@@ -2953,14 +2971,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490121</v>
+        <v>490054</v>
       </c>
       <c r="R23" t="n">
-        <v>6848345</v>
+        <v>6848206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,13 +3036,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431652</t>
+          <t>https://artportalen.se/Sighting/135430855</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135431942</v>
+        <v>135431313</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3055,14 +3073,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490110</v>
+        <v>490147</v>
       </c>
       <c r="R24" t="n">
-        <v>6848436</v>
+        <v>6848240</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,13 +3138,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431942</t>
+          <t>https://artportalen.se/Sighting/135431313</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135432247</v>
+        <v>135431477</v>
       </c>
       <c r="B25" t="n">
         <v>99276</v>
@@ -3154,17 +3172,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490053</v>
+        <v>490169</v>
       </c>
       <c r="R25" t="n">
-        <v>6848327</v>
+        <v>6848351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,13 +3249,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135432247</t>
+          <t>https://artportalen.se/Sighting/135431477</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135432573</v>
+        <v>135431652</v>
       </c>
       <c r="B26" t="n">
         <v>99276</v>
@@ -3256,26 +3283,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489761</v>
+        <v>490121</v>
       </c>
       <c r="R26" t="n">
-        <v>6848218</v>
+        <v>6848345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,51 +3351,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135432573</t>
+          <t>https://artportalen.se/Sighting/135431652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135430638</v>
+        <v>135431942</v>
       </c>
       <c r="B27" t="n">
-        <v>99194</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490014</v>
+        <v>490110</v>
       </c>
       <c r="R27" t="n">
-        <v>6848138</v>
+        <v>6848436</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,51 +3453,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430638</t>
+          <t>https://artportalen.se/Sighting/135431942</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135430729</v>
+        <v>135432247</v>
       </c>
       <c r="B28" t="n">
-        <v>99194</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489990</v>
+        <v>490053</v>
       </c>
       <c r="R28" t="n">
-        <v>6848135</v>
+        <v>6848327</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,51 +3555,60 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430729</t>
+          <t>https://artportalen.se/Sighting/135432247</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135430884</v>
+        <v>135432573</v>
       </c>
       <c r="B29" t="n">
-        <v>99194</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490064</v>
+        <v>489761</v>
       </c>
       <c r="R29" t="n">
-        <v>6848204</v>
+        <v>6848218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3638,6 +3665,534 @@
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432573</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136042898</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98160</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>489802</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6848139</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042898</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136042903</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98160</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>489768</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6848103</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042903</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135430638</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99194</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6848138</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430638</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135430729</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99194</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6848135</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430729</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135430884</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99194</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6848204</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135430884</t>
         </is>
@@ -3673,6 +4228,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
